--- a/reports/Debug-purgatory-20260104/For The Week Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Week Ending (Actual)_Revenue.xlsx
@@ -76,12 +76,12 @@
     <t>T103</t>
   </si>
   <si>
+    <t>T105</t>
+  </si>
+  <si>
     <t>T100</t>
   </si>
   <si>
-    <t>T105</t>
-  </si>
-  <si>
     <t>department</t>
   </si>
   <si>
@@ -100,7 +100,7 @@
     <t>D4053</t>
   </si>
   <si>
-    <t>D4054</t>
+    <t xml:space="preserve">D4054                    </t>
   </si>
   <si>
     <t>D4055</t>
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>1344987.3700</v>
+        <v>22359.0000</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -561,7 +561,7 @@
         <v>23</v>
       </c>
       <c r="D4" s="2">
-        <v>22359.0000</v>
+        <v>1344987.3700</v>
       </c>
     </row>
     <row r="5" spans="1:4">
